--- a/EstablecimientoSalud/excels/TACNA-TACNA-TACNA.xlsx
+++ b/EstablecimientoSalud/excels/TACNA-TACNA-TACNA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>2922</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-18.06886603</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>10190</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-18.01367</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2923</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-18.0196822</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>2906</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>230111</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LA YARADA LOS PALOS</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-18.20842309</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2917</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-18.00060548</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>2918</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-18.01252003</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>31651</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-18.0069283</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2892</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>230103</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CALANA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-17.94405496</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>11195</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-18.00919833</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>2883</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>230102</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ALTO DE LA ALIANZA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-17.99417176</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>2908</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>230111</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LA YARADA LOS PALOS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-18.29243101</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>10228</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-18.00277917</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>27954</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-18.03546375</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>11528</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-18.01568584</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>2920</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-18.03370906</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>2919</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-18.0000716</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>2907</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>230111</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LA YARADA LOS PALOS</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-18.33541629</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>2895</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>230106</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PACHIA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-17.64423116</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>26594</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-18.01681575</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>230101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>12021</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>230101</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-18.02588781</t>
@@ -1722,11 +1622,6 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>230101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/TACNA-TACNA-TACNA.xlsx
+++ b/EstablecimientoSalud/excels/TACNA-TACNA-TACNA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
